--- a/output/Result_Report.xlsx
+++ b/output/Result_Report.xlsx
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>522</v>
+        <v>475</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>20426.26</v>
+        <v>17624.26</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>17.01</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="27">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>589</v>
+        <v>522</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>35771.68</v>
+        <v>36294.77</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>29.8</v>
+        <v>30.23</v>
       </c>
     </row>
     <row r="28">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3469.93</v>
+        <v>5748.84</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2.89</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="29">
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>656</v>
+        <v>576</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>41533.88</v>
+        <v>36846.38</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>34.59</v>
+        <v>30.69</v>
       </c>
     </row>
     <row r="32">
@@ -1078,13 +1078,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>163</v>
+        <v>243</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>6765.650000000001</v>
+        <v>11453.15</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>5.64</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -1512,11 +1512,11 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>31-90</t>
+          <t>91-180</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1704,11 +1704,11 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>31-90</t>
+          <t>91-180</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="L18" s="3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -2344,11 +2344,11 @@
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>0-30</t>
+          <t>31-90</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
@@ -2984,11 +2984,11 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>31-90</t>
+          <t>91-180</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="L36" s="3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="L37" s="3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="L38" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         </is>
       </c>
       <c r="L39" s="3" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
@@ -4032,31 +4032,31 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2554.71</v>
+        <v>8428.869999999999</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2.13</v>
+        <v>7.02</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>386</v>
+        <v>269</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>19899.74</v>
+        <v>16827.58</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>16.58</v>
+        <v>14.02</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>2802</v>
+        <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>520</v>
@@ -4148,22 +4148,22 @@
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1783.93</v>
+        <v>2876.18</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.49</v>
+        <v>2.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>17801.06</v>
+        <v>16708.81</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>14.83</v>
+        <v>13.92</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>160</v>
